--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>노프짐 춘천점</t>
+          <t>노프짐 춘��점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fnql010@naver.com</t>
+          <t>yodavely@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1425,6 +1425,104 @@
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>포나인필라테스 평생교육원</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>four9_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1468-9920</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://litt.ly/four9pilates</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49y8c</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>166</v>
+      </c>
+      <c r="R11" t="n">
+        <v>334</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1134526090</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134526090</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="Q2" t="n">
-        <v>471</v>
+        <v>516</v>
       </c>
       <c r="R2" t="n">
-        <v>851</v>
+        <v>911</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨에스짐</t>
+          <t>노벨짐24 후평점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>csgym114@naver.com</t>
+          <t>coduswnsla@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1347-6320</t>
+          <t>0507-1491-7766</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 춘천시 세실로 114 2층</t>
+          <t>강원 춘천시 후석로 247 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/csgym114</t>
+          <t>https://blog.naver.com/coduswnsla</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc0i3i</t>
+          <t>https://talk.naver.com/ct/w6w32mj</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,17 +719,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>350</v>
+        <v>528</v>
       </c>
       <c r="Q3" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="R3" t="n">
-        <v>465</v>
+        <v>678</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1180314397</t>
+          <t>2048252376</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180314397</t>
+          <t>https://m.place.naver.com/place/2048252376</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>렉슬휘트니스 헬스&amp;PT 우두점</t>
+          <t>씨에스짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rexlefitness@naver.com</t>
+          <t>csgym114@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1403-3725</t>
+          <t>0507-1347-6320</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 충열로 45 6층</t>
+          <t>강원 춘천시 세실로 114 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rexlefitness/</t>
+          <t>https://blog.naver.com/csgym114</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wd0i63j</t>
+          <t>https://talk.naver.com/ct/wc0i3i</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="Q4" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="R4" t="n">
-        <v>189</v>
+        <v>465</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36651112</t>
+          <t>1180314397</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36651112</t>
+          <t>https://m.place.naver.com/place/1180314397</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,39 +858,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>노프짐 춘��점</t>
+          <t>브레이브힐 사농점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>noffgym@naver.com</t>
+          <t>2014bravehill@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1305-1277</t>
+          <t>0507-1342-5155</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+          <t>강원 춘천시 사우4길 36 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noffgym</t>
+          <t>http://bravehill2014.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,14 +900,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pbe</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,17 +911,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="Q5" t="n">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>312</v>
+        <v>147</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1931931002</t>
+          <t>1933437118</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931931002</t>
+          <t>https://m.place.naver.com/place/1933437118</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>썬더짐</t>
+          <t>노프짐 춘천점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hth8307@naver.com</t>
+          <t>noffgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1311-9764</t>
+          <t>0507-1305-1277</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 영서로 1745-7 썬더짐</t>
+          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thundergym_official</t>
+          <t>https://blog.naver.com/noffgym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,18 +989,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42pbe</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1948</v>
+        <v>168</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="R6" t="n">
-        <v>2028</v>
+        <v>315</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1875414500</t>
+          <t>1931931002</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875414500</t>
+          <t>https://m.place.naver.com/place/1931931002</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스 &amp; PT 굿리프트</t>
+          <t>올라운더피트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goodlift_hong@naver.com</t>
+          <t>leedydrud1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1441-6464</t>
+          <t>033-241-2003</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 춘천시 효석로 37 1층</t>
+          <t>강원 춘천시 후석로 246 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/goodlift_cc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpxy8r2</t>
+          <t>https://talk.naver.com/ct/w3rfbs7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="Q7" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1966374826</t>
+          <t>1406326621</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966374826</t>
+          <t>https://m.place.naver.com/place/1406326621</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1503</v>
+        <v>1518</v>
       </c>
       <c r="Q8" t="n">
         <v>52</v>
       </c>
       <c r="R8" t="n">
-        <v>1555</v>
+        <v>1570</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1328,203 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>아베크짐</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>wannabe-pt@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1340-0660</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://open.kakao.com/o/sFMuVPdh</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zpx4</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>356</v>
-      </c>
-      <c r="R10" t="n">
-        <v>412</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1147379761</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1147379761</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>포나인필라테스 평생교육원</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>four9_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1468-9920</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://litt.ly/four9pilates</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49y8c</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>166</v>
-      </c>
-      <c r="R11" t="n">
-        <v>334</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1134526090</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1134526090</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q2" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="R2" t="n">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="Q8" t="n">
         <v>52</v>
       </c>
       <c r="R8" t="n">
-        <v>1570</v>
+        <v>1577</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -1143,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>렉슬프로짐</t>
+          <t>썬더짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rexleprogym@naver.com</t>
+          <t>hth8307@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1442-9688</t>
+          <t>0507-1311-9764</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
+          <t>강원 춘천시 동내면 영서로 1745-7 썬더짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rexleprogym</t>
+          <t>https://www.instagram.com/thundergym_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,22 +1185,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7k39ti</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1525</v>
+        <v>1959</v>
       </c>
       <c r="Q8" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="R8" t="n">
-        <v>1577</v>
+        <v>2039</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1421522019</t>
+          <t>1875414500</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421522019</t>
+          <t>https://m.place.naver.com/place/1875414500</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,87 +1242,283 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>올핀트레이닝센터</t>
+          <t>렉슬프로짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yodavely@naver.com</t>
+          <t>rexleprogym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>033-910-0340</t>
+          <t>0507-1442-9688</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rexleprogym</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7k39ti</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1525</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>52</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1577</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1421522019</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421522019</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>올핀트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yodavely@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>033-910-0340</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>강원 춘천시 경춘로 2354 7층 701호</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://www.instagram.com/allinone_infinity</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>74</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>40</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>114</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>1367250279</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1367250279</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>포나인필라테스 평생교육원</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>four9_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1468-9920</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://litt.ly/four9pilates</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49y8c</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>168</v>
+      </c>
+      <c r="R11" t="n">
+        <v>336</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1134526090</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134526090</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="Q8" t="n">
         <v>80</v>
       </c>
       <c r="R8" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>렉슬프로짐</t>
+          <t>헬스 &amp; PT 굿리프트</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rexleprogym@naver.com</t>
+          <t>goodlift_hong@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1442-9688</t>
+          <t>0507-1441-6464</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
+          <t>강원 춘천시 효석로 37 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rexleprogym</t>
+          <t>https://smartstore.naver.com/goodlift_cc</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7k39ti</t>
+          <t>https://talk.naver.com/ct/wpxy8r2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1525</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="R9" t="n">
-        <v>1577</v>
+        <v>108</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1421522019</t>
+          <t>1966374826</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421522019</t>
+          <t>https://m.place.naver.com/place/1966374826</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>올핀트레이닝센터</t>
+          <t>렉슬프로짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yodavely@naver.com</t>
+          <t>rexleprogym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>033-910-0340</t>
+          <t>0507-1442-9688</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 춘천시 경춘로 2354 7층 701호</t>
+          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allinone_infinity</t>
+          <t>https://blog.naver.com/rexleprogym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,15 +1377,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7k39ti</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>1527</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="R10" t="n">
-        <v>114</v>
+        <v>1579</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1367250279</t>
+          <t>1421522019</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1367250279</t>
+          <t>https://m.place.naver.com/place/1421522019</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,96 +1433,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포나인필라테스 평생교육원</t>
+          <t>올핀트레이닝센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>four9_pilates@naver.com</t>
+          <t>yodavely@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1468-9920</t>
+          <t>033-910-0340</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>강원 춘천시 경춘로 2354 7층 701호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allinone_infinity</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>40</v>
+      </c>
+      <c r="R11" t="n">
+        <v>114</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1367250279</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1367250279</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>포나인필라테스 평생교육원</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>four9_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1468-9920</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://litt.ly/four9pilates</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w49y8c</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>168</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>168</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>336</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1134526090</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1134526090</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="Q10" t="n">
         <v>52</v>
       </c>
       <c r="R10" t="n">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1519,104 +1519,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>포나인필라테스 평생교육원</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>four9_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1468-9920</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://litt.ly/four9pilates</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49y8c</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>168</v>
-      </c>
-      <c r="R12" t="n">
-        <v>336</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1134526090</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1134526090</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>398</v>
       </c>
       <c r="Q2" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="R2" t="n">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>씨에스짐</t>
+          <t>크로스핏 펄스온</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>csgym114@naver.com</t>
+          <t>crossfitblank@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1347-6320</t>
+          <t>0507-1368-9628</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 세실로 114 2층</t>
+          <t>강원 춘천시 안마산로 224-2 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/csgym114</t>
+          <t>https://www.instagram.com/pulseon_cf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc0i3i</t>
+          <t>https://talk.naver.com/ct/wpvteqn</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>465</v>
+        <v>28</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1180314397</t>
+          <t>2070790798</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180314397</t>
+          <t>https://m.place.naver.com/place/2070790798</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q5" t="n">
         <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>올라운더피트니스</t>
+          <t>노프짐 춘천점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leedydrud1@naver.com</t>
+          <t>noffgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>033-241-2003</t>
+          <t>0507-1305-1277</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 후석로 246 3층</t>
+          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/noffgym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3rfbs7</t>
+          <t>https://talk.naver.com/ct/w42pbe</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="R6" t="n">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1406326621</t>
+          <t>1931931002</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406326621</t>
+          <t>https://m.place.naver.com/place/1931931002</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>썬더짐</t>
+          <t>올라운더피트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hth8307@naver.com</t>
+          <t>leedydrud1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1311-9764</t>
+          <t>033-241-2003</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 영서로 1745-7 썬더짐</t>
+          <t>강원 춘천시 후석로 246 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thundergym_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,28 +1092,32 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3rfbs7</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1960</v>
+        <v>188</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2040</v>
+        <v>188</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1875414500</t>
+          <t>1406326621</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875414500</t>
+          <t>https://m.place.naver.com/place/1406326621</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스 &amp; PT 굿리프트</t>
+          <t>렉슬프로짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>goodlift_hong@naver.com</t>
+          <t>rexleprogym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1441-6464</t>
+          <t>0507-1442-9688</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 효석로 37 1층</t>
+          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/goodlift_cc</t>
+          <t>https://blog.naver.com/rexleprogym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpxy8r2</t>
+          <t>https://talk.naver.com/ct/w7k39ti</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>1531</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="R8" t="n">
-        <v>108</v>
+        <v>1583</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1966374826</t>
+          <t>1421522019</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966374826</t>
+          <t>https://m.place.naver.com/place/1421522019</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1331,39 +1335,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>렉슬프로짐</t>
+          <t>포나인필라테스 평생교육원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rexleprogym@naver.com</t>
+          <t>four9_pilates@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1442-9688</t>
+          <t>0507-1468-9920</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
+          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rexleprogym</t>
+          <t>https://litt.ly/four9pilates</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7k39ti</t>
+          <t>https://talk.naver.com/ct/w49y8c</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1531</v>
+        <v>168</v>
       </c>
       <c r="Q10" t="n">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="R10" t="n">
-        <v>1583</v>
+        <v>336</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,113 +1416,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1421522019</t>
+          <t>1134526090</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421522019</t>
+          <t>https://m.place.naver.com/place/1134526090</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>포나인필라테스 평생교육원</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>four9_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1468-9920</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://litt.ly/four9pilates</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49y8c</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>168</v>
-      </c>
-      <c r="R11" t="n">
-        <v>336</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1134526090</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1134526090</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q2" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="R2" t="n">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="Q3" t="n">
         <v>150</v>
       </c>
       <c r="R3" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+          <t>강원 춘천시 동내면 춘천순환�� 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1328,105 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>포나인필라테스 평생교육원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>four9_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1468-9920</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://litt.ly/four9pilates</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49y8c</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>168</v>
-      </c>
-      <c r="R10" t="n">
-        <v>336</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1134526090</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1134526090</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q2" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="R2" t="n">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Q3" t="n">
         <v>150</v>
       </c>
       <c r="R3" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>크로스핏 펄스온</t>
+          <t>청년헬스 후평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>crossfitblank@naver.com</t>
+          <t>jth3824@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-9628</t>
+          <t>0507-1381-6789</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 224-2 1층</t>
+          <t>강원 춘천시 백령로 178 금성빌딩4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pulseon_cf</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpvteqn</t>
+          <t>https://talk.naver.com/ct/wcfc19</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="R4" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2070790798</t>
+          <t>1866336888</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070790798</t>
+          <t>https://m.place.naver.com/place/1866336888</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -969,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 춘천순환�� 63 명일빌딩 3층 노프짐</t>
+          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6" t="n">
         <v>147</v>
       </c>
       <c r="R6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="Q8" t="n">
         <v>52</v>
       </c>
       <c r="R8" t="n">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1327,6 +1327,104 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>포나인필라테스 평생교육원</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>four9_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1468-9920</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://litt.ly/four9pilates</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49y8c</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>168</v>
+      </c>
+      <c r="R10" t="n">
+        <v>336</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1134526090</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134526090</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q2" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R2" t="n">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Q3" t="n">
         <v>150</v>
       </c>
       <c r="R3" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1328,105 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>포나인필라테스 평생교육원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>four9_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1468-9920</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 퇴계로 249 405호, 크리스탈빌딩</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://litt.ly/four9pilates</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49y8c</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>168</v>
-      </c>
-      <c r="R10" t="n">
-        <v>336</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1134526090</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1134526090</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/춘천_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>노벨짐 석사점</t>
+          <t>렉슬프로짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sodkwk@naver.com</t>
+          <t>rexleprogym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1382-7834</t>
+          <t>0507-1442-9688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 춘천시 지석로 85 강남프라자 4층</t>
+          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sodkwk</t>
+          <t>https://blog.naver.com/rexleprogym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2al29z</t>
+          <t>https://talk.naver.com/ct/w7k39ti</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>405</v>
+        <v>1533</v>
       </c>
       <c r="Q2" t="n">
-        <v>533</v>
+        <v>52</v>
       </c>
       <c r="R2" t="n">
-        <v>938</v>
+        <v>1585</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2076990312</t>
+          <t>1421522019</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076990312</t>
+          <t>https://m.place.naver.com/place/1421522019</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>노벨짐24 후평점</t>
+          <t>올핀트레이닝센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>coduswnsla@naver.com</t>
+          <t>yodavely@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1491-7766</t>
+          <t>033-910-0340</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 춘천시 후석로 247 6층</t>
+          <t>강원 춘천시 경춘로 2354 7층 701호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coduswnsla</t>
+          <t>https://www.instagram.com/allinone_infinity</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,634 +699,50 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6w32mj</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R3" t="n">
+        <v>114</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>533</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>150</v>
-      </c>
-      <c r="R3" t="n">
-        <v>683</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2048252376</t>
+          <t>1367250279</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2048252376</t>
+          <t>https://m.place.naver.com/place/1367250279</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>청년헬스 후평점</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>jth3824@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1381-6789</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>강원 춘천시 백령로 178 금성빌딩4층</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfc19</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>36</v>
-      </c>
-      <c r="R4" t="n">
-        <v>51</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1866336888</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1866336888</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>브레이브힐 사농점</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2014bravehill@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1342-5155</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>강원 춘천시 사우4길 36 3층</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>http://bravehill2014.com/</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>35</v>
-      </c>
-      <c r="R5" t="n">
-        <v>149</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1933437118</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1933437118</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>노프짐 춘천점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>noffgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1305-1277</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/noffgym</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pbe</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>169</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>147</v>
-      </c>
-      <c r="R6" t="n">
-        <v>316</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1931931002</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1931931002</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>올라운더피트니스</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>leedydrud1@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>033-241-2003</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>강원 춘천시 후석로 246 3층</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3rfbs7</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>189</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>189</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1406326621</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1406326621</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>렉슬프로짐</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>rexleprogym@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1442-9688</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/rexleprogym</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7k39ti</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1533</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>52</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1585</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1421522019</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1421522019</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>올핀트레이닝센터</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yodavely@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>033-910-0340</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>강원 춘천시 경춘로 2354 7층 701호</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/allinone_infinity</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R9" t="n">
-        <v>114</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1367250279</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1367250279</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
